--- a/output/pdf_financials_xlsx/CMI.xlsx
+++ b/output/pdf_financials_xlsx/CMI.xlsx
@@ -2563,46 +2563,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.939604</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.104967</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.002455</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>8.129115000000001</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>6.041775</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>3.465578</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>4.302834</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>5.322102</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>6.783758</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>8.882927</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>10.130841</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>5.48236</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>5.89044</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>4.957214</v>
       </c>
     </row>
     <row r="35">
@@ -2661,46 +2661,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>2.50242</v>
+        <v>4.442024</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>4.119363</v>
+        <v>5.22433</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>3.798643</v>
+        <v>6.801098</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>2.835358</v>
+        <v>10.964473</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>10.08113</v>
+        <v>16.122905</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>11.625543</v>
+        <v>15.091121</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>11.804495</v>
+        <v>16.107329</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>9.857946</v>
+        <v>15.180048</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>8.074676</v>
+        <v>14.858434</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>8.190685999999999</v>
+        <v>17.073613</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>8.720656999999999</v>
+        <v>18.851498</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>9.958482</v>
+        <v>15.440842</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>10.05</v>
+        <v>15.94044</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>10.860959</v>
+        <v>15.818173</v>
       </c>
     </row>
     <row r="37">
@@ -3249,46 +3249,46 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.320103</v>
+        <v>0.380499</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.624556</v>
+        <v>0.519589</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.330513</v>
+        <v>0.328058</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>8.159414</v>
+        <v>0.030299</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>6.467477</v>
+        <v>0.425702</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.716441</v>
+        <v>0.250863</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>4.398566</v>
+        <v>0.095732</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>5.403527</v>
+        <v>0.081425</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>7.140883</v>
+        <v>0.357125</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>9.077171999999999</v>
+        <v>0.194245</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>9.97241</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>5.617632</v>
+        <v>0.135272</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>7.179572</v>
+        <v>1.289132</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>6.69815</v>
+        <v>1.740936</v>
       </c>
     </row>
     <row r="49">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -13162,7 +13162,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">

--- a/output/pdf_financials_xlsx/CMI.xlsx
+++ b/output/pdf_financials_xlsx/CMI.xlsx
@@ -1897,35 +1897,23 @@
       <c r="I23" s="3" t="n">
         <v>2.843092</v>
       </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J23" s="3" t="n">
+        <v>-0.213392</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>1.422821</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>1.139655</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>1.672907</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>-0.211475</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>-0.40755</v>
       </c>
     </row>
     <row r="24">
@@ -4083,40 +4071,40 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.872497</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.756863</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.708028</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.8020659999999999</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.656681</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.307006</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.399061</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.653596</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.512942</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.478876</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.472067</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.235666</v>
       </c>
     </row>
     <row r="65">
@@ -4230,40 +4218,40 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.276701</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.419047</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.129116</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.192562</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.288586</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.148545</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.422507</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.718713</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.595664</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.384233</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.434598</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.419024</v>
       </c>
     </row>
     <row r="68">
@@ -4407,10 +4395,10 @@
         <v>0</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.275547</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.298561</v>
       </c>
     </row>
     <row r="71">
@@ -4456,10 +4444,10 @@
         <v>0</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.275547</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.298561</v>
       </c>
     </row>
     <row r="72">
@@ -4652,10 +4640,10 @@
         <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.181944</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.147466</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4799,10 +4787,10 @@
         <v>0</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0</v>
+        <v>1.220404</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0</v>
+        <v>0.921843</v>
       </c>
     </row>
     <row r="79">
@@ -4848,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>0</v>
+        <v>1.220404</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>0</v>
+        <v>0.921843</v>
       </c>
     </row>
     <row r="80">
@@ -4920,15 +4908,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N80" s="3" t="n">
+        <v>0.06350524701697043</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.05229698005213568</v>
       </c>
     </row>
     <row r="81">
@@ -5170,10 +5154,10 @@
         <v>0.09360300000000001</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>1.314007</v>
+        <v>0.09360300000000001</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>1.072938</v>
+        <v>0.151095</v>
       </c>
     </row>
     <row r="86">
@@ -5827,35 +5811,23 @@
       <c r="I99" s="3" t="n">
         <v>2.843092</v>
       </c>
-      <c r="J99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J99" s="3" t="n">
+        <v>-0.213392</v>
+      </c>
+      <c r="K99" s="3" t="n">
+        <v>1.422821</v>
+      </c>
+      <c r="L99" s="3" t="n">
+        <v>1.139655</v>
+      </c>
+      <c r="M99" s="3" t="n">
+        <v>1.672907</v>
+      </c>
+      <c r="N99" s="3" t="n">
+        <v>-0.211475</v>
+      </c>
+      <c r="O99" s="3" t="n">
+        <v>-0.40755</v>
       </c>
     </row>
     <row r="100">
@@ -8856,7 +8828,11 @@
           <t>Lease obligations 13</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -9192,7 +9168,11 @@
           <t>Lease obligations 13</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -20612,7 +20592,11 @@
           <t>Net income / (loss) $</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -24596,7 +24580,11 @@
           <t>Future income tax expense</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E208" s="5" t="n">
         <v>0.15589</v>
       </c>
